--- a/docs/00_기획/유니티_커리큘럼_7개월.xlsx
+++ b/docs/00_기획/유니티_커리큘럼_7개월.xlsx
@@ -128,7 +128,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -515,7 +515,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -529,7 +529,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="2" ht="216" customHeight="1">
+    <row r="2" ht="192" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>1개월</t>
@@ -543,17 +543,17 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t>[ 개발 환경 구축 ]
-- 과정 소개 및 최종 결과물(2인 협동 웨이브 디펜스) 시연
-- 유니티 및 Visual Studio 설치
-- C# 콘솔 프로젝트 생성 및 실행
+   • 과정 소개 및 최종 결과물(2인 협동 로그라이크) 시연
+   • 유니티 및 Visual Studio 설치
+   • C# 콘솔 프로젝트 생성 및 실행
 [ C# 프로그램의 기본 구조 ]
-- Main 메서드와 프로그램 실행 흐름
-- Console.WriteLine을 활용한 출력
-- 주석 작성과 세미콜론·중괄호 규칙
+   • Main 메서드와 프로그램 실행 흐름
+   • Console.WriteLine을 활용한 출력
+   • 주석 작성과 세미콜론·중괄호 규칙
 [ 변수와 자료형 ]
-- 변수의 개념과 선언
-- 기본 자료형(int, float, double, bool, char, string) 이해
-- Console.ReadLine을 활용한 입력</t>
+   • 변수의 개념과 선언
+   • 기본 자료형(int, float, double, bool, char, string) 이해
+   • Console.ReadLine을 활용한 입력</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -563,7 +563,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="180" customHeight="1">
+    <row r="3" ht="161" customHeight="1">
       <c r="A3" s="6" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -573,20 +573,20 @@
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t>[ 자료형 심화 ]
-- 형 변환(암시적·명시적)과 Parse / Convert
-- 상수(const)의 개념과 활용
+   • 형 변환(암시적·명시적)과 Parse / Convert
+   • 상수(const)의 개념과 활용
 [ 연산자 활용 ]
-- 산술 연산자와 대입 연산자
-- 비교 연산자와 논리 연산자
-- 연산자 우선순위
+   • 산술 연산자와 대입 연산자
+   • 비교 연산자와 논리 연산자
+   • 연산자 우선순위
 [ 오류 대응 ]
-- 컴파일 에러 메시지 해석 (파일명·줄 번호 확인)
-- 자주 발생하는 문법 오류 유형 정리</t>
+   • 컴파일 에러 메시지 해석 (파일명·줄 번호 확인)
+   • 자주 발생하는 문법 오류 유형 정리</t>
         </is>
       </c>
       <c r="D3" s="6" t="n"/>
     </row>
-    <row r="4" ht="180" customHeight="1">
+    <row r="4" ht="161" customHeight="1">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -596,20 +596,20 @@
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t>[ 조건문 학습 ]
-- if / else if / else 구조
-- 중첩 조건문
-- switch 문 활용
+   • if / else if / else 구조
+   • 중첩 조건문
+   • switch 문 활용
 [ 반복문 학습 ]
-- for 문 구조와 활용
-- while / do-while 문
-- break와 continue
+   • for 문 구조와 활용
+   • while / do-while 문
+   • break와 continue
 [ 콘솔 실습 ]
-- 숫자 맞히기, 구구단, 간단한 계산기 제작</t>
+   • 체력·데미지 계산기, 구구단, 숫자 맞히기 제작</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
     </row>
-    <row r="5" ht="234" customHeight="1">
+    <row r="5" ht="207.5" customHeight="1">
       <c r="A5" s="7" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>[ 배열과 컬렉션 ]
-- 배열의 기본 구조 이해
-- 2차원 배열
-- List의 개념과 활용
+   • 배열의 기본 구조 이해
+   • 2차원 배열
+   • List의 개념과 활용
 [ 함수(메서드)의 기본 구조 ]
-- 메서드 정의와 호출
-- 매개변수와 반환값
-- 메서드 오버로딩
+   • 메서드 정의와 호출
+   • 매개변수와 반환값
+   • 메서드 오버로딩
 [ Visual Studio 코드 디버깅 ]
-- 중단점 설정 및 단계별 실행
-- 변수값 확인과 오류 원인 분석 기초
+   • 중단점 설정 및 단계별 실행
+   • 변수값 확인과 오류 원인 분석 기초
 [ 1개월차 종합 평가 ]
-- 콘솔 미니 프로그램 단독 제작</t>
+   • 콘솔 미니 프로그램 단독 제작</t>
         </is>
       </c>
       <c r="D5" s="7" t="n"/>
     </row>
-    <row r="6" ht="144" customHeight="1">
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2개월</t>
@@ -649,13 +649,13 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>[ 객체지향 기초 문법 학습 ]
-- 클래스와 객체의 개념 이해
-- 필드와 메서드
-- 생성자와 인스턴스 생성
-- 접근제한자(private / public / protected)
-- property 문법 이해
+   • 클래스와 객체의 개념 이해
+   • 필드와 메서드
+   • 생성자와 인스턴스 생성
+   • 접근제한자(private / public / protected)
+   • property 문법 이해
 [ 콘솔 실습 ]
-- 클래스를 활용한 캐릭터 정보 관리 프로그램</t>
+   • 클래스를 활용한 캐릭터 정보 관리 프로그램</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -665,7 +665,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="144" customHeight="1">
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -675,18 +675,18 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>[ 객체지향 문법 심화 ]
-- 상속의 개념과 활용
-- virtual / override를 활용한 다형성 학습
-- 인터페이스의 개념과 활용
-- 열거형(enum)의 개념과 활용
-- static 변수와 정적 멤버 활용
+   • 상속의 개념과 활용
+   • virtual / override를 활용한 다형성 학습
+   • 인터페이스의 개념과 활용
+   • 열거형(enum)의 개념과 활용
+   • static 변수와 정적 멤버 활용
 [ 콘솔 실습 ]
-- 상속·인터페이스를 활용한 몬스터 클래스 설계</t>
+   • 상속·인터페이스를 활용한 몬스터 클래스 설계</t>
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
     </row>
-    <row r="8" ht="198" customHeight="1">
+    <row r="8" ht="207.5" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -695,22 +695,24 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>[ 유니티 개발 환경 및 기본 기능 이해 ]
-- 유니티 프로젝트 생성 및 핵심 인터페이스 익히기
-- GameObject와 Component의 관계 이해
-- Transform 컴포넌트
-- Rigidbody를 활용한 물리 실습
-- Play 모드와 편집 모드 구분
-[ 유니티에서의 C# ]
-- MonoBehaviour와 스크립트 부착
-- Start / Update 생명주기 이해
-- Debug.Log와 Console 창 활용
-- [SerializeField]를 활용한 변수 설정</t>
+          <t>[ 유니티 에디터 적응 ]
+   • 유니티 프로젝트 생성 및 핵심 인터페이스 익히기
+   • Inspector 창의 구조와 값 조정
+   • Scene 뷰 조작과 오브젝트 탐색
+[ Transform 컴포넌트 ]
+   • Position과 좌표계 이해
+   • Rotation · Scale
+   • 부모-자식 관계와 로컬/월드 좌표
+[ GameObject와 Component ]
+   • GameObject와 Component의 관계 이해
+   • Component 추가·제거 실습
+   • Play 모드와 편집 모드 구분
+   • 7주차 종합 실습 및 자가진단</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
     </row>
-    <row r="9" ht="126" customHeight="1">
+    <row r="9" ht="192" customHeight="1">
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -719,18 +721,23 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[ 유니티의 기본 기능 실습 ]
-- transform.position을 활용한 오브젝트 이동
-- Vector2 / Vector3 방향 벡터 이해
-- 입력값을 활용한 Player 이동 구현
-- Time.deltaTime을 활용한 프레임 독립 처리
-- GameObject 활성화 및 비활성화
-- [ContextMenu] 속성 활용</t>
+          <t>[ 유니티에서의 C# ]
+   • MonoBehaviour와 스크립트 부착
+   • Start / Update 생명주기 이해
+   • Debug.Log와 Console 창 활용
+   • [SerializeField]를 활용한 변수 설정
+[ 유니티의 기본 기능 실습 ]
+   • transform.position을 활용한 오브젝트 이동
+   • Vector2 / Vector3 방향 벡터 이해
+   • Time.deltaTime을 활용한 프레임 독립 처리
+   • 입력값을 활용한 Player 이동 구현
+   • GameObject 활성화 및 비활성화
+   • [ContextMenu] 속성 활용</t>
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
     </row>
-    <row r="10" ht="144" customHeight="1">
+    <row r="10" ht="161" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>3개월</t>
@@ -744,13 +751,15 @@
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t>[ 유니티 2D 물리 ]
-- Rigidbody2D 컴포넌트 이해
-- 물리 기반 Player 이동 구현
-- Collider2D와 isTrigger 차이
+   • Rigidbody2D 컴포넌트 이해
+   • 물리 기반 Player 이동 구현
+   • Collider2D와 isTrigger 차이
 [ 충돌 처리 ]
-- OnTriggerEnter2D / OnCollisionEnter2D 활용
-- Tag를 활용한 충돌 대상 구분
-- Layer 및 Layer Collision Matrix 설정</t>
+   • OnTriggerEnter2D / OnCollisionEnter2D 활용
+   • Tag를 활용한 충돌 대상 구분
+   • Layer 및 Layer Collision Matrix 설정
+[ 2D 렌더링 ]
+   • Sorting Layer와 Order in Layer</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -760,7 +769,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="144" customHeight="1">
+    <row r="11" ht="130" customHeight="1">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -770,18 +779,18 @@
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t>[ 오브젝트 동적 생성 ]
-- Prefab의 개념과 활용 방법 익히기
-- Instantiate를 활용한 총알 발사 구현
-- 몬스터 GameObject 동적 생성
-- Destroy와 오브젝트 수명 관리
+   • Prefab의 개념과 활용 방법 익히기
+   • Instantiate를 활용한 총알 발사 구현
+   • 몬스터 GameObject 동적 생성
+   • Destroy와 오브젝트 수명 관리
 [ 컴포넌트 참조 ]
-- GetComponent를 활용한 타 오브젝트 제어
-- 체력 시스템 및 피격 처리 구현</t>
+   • GetComponent를 활용한 타 오브젝트 제어
+   • 체력 시스템 및 피격 처리 구현</t>
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
     </row>
-    <row r="12" ht="144" customHeight="1">
+    <row r="12" ht="130" customHeight="1">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -791,18 +800,18 @@
       <c r="C12" s="4" t="inlineStr">
         <is>
           <t>[ 코루틴 ]
-- IEnumerator와 yield 이해
-- WaitForSeconds를 활용한 시간차 처리
-- 일정 간격 몬스터 스폰 구현
+   • IEnumerator와 yield 이해
+   • WaitForSeconds를 활용한 시간차 처리
+   • 일정 간격 몬스터 스폰 구현
 [ 스프라이트와 애니메이션 기초 ]
-- Sprite 설정 및 Animator 기본 이해
+   • Sprite 설정 및 Animator 기본 이해
 [ 미니게임 ① 피하기 게임 ]
-- 장애물 생성 및 회피 구현</t>
+   • 장애물 생성 및 회피 구현</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
     </row>
-    <row r="13" ht="108" customHeight="1">
+    <row r="13" ht="99" customHeight="1">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -812,16 +821,16 @@
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>[ 미니게임 ① 완성 ]
-- 점수 및 게임오버 처리
-- 개인 개조 및 시연
+   • 점수 및 게임오버 처리
+   • 개인 개조 및 시연
 [ 미니게임 ② 벽돌깨기 ]
-- 배열을 활용한 블록 배치
-- 반사 처리 및 클리어 판정</t>
+   • 배열을 활용한 블록 배치
+   • 반사 처리 및 클리어 판정</t>
         </is>
       </c>
       <c r="D13" s="7" t="n"/>
     </row>
-    <row r="14" ht="108" customHeight="1">
+    <row r="14" ht="99" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>4개월</t>
@@ -835,11 +844,11 @@
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t>[ 미니게임 ② 완성 및 개조 ]
-- 개인 개조 및 시연
-[ 미니게임 ③ 웨이브 슈팅 ]
-- 웨이브 개념 이해
-- 적 스폰 · 체력 · 게임오버 구현
-- 미니게임 3종 시연 발표</t>
+   • 개인 개조 및 시연
+[ 미니게임 ③ 생존 슈팅 ]
+   • 지속 스폰 개념 이해
+   • 적 스폰 · 체력 · 게임오버 구현
+   • 미니게임 3종 시연 발표</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -849,7 +858,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="144" customHeight="1">
+    <row r="15" ht="161" customHeight="1">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -859,18 +868,20 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t>[ 본 프로젝트 착수 ]
-- 프로젝트 구조 설계 및 에셋 패키지 임포트
+   • 프로젝트 구조 설계 및 에셋 패키지 임포트
+[ 플레이어와 카메라 ]
+   • 플레이어 이동 및 애니메이션 연결
+   • 카메라 추적 구현
+[ 무한 맵 ]
+   • 바닥 타일 순환 방식의 무한 맵 구현
+   • 카메라 기준 타일 재배치 로직
 [ 객체지향 설계 적용 ]
-- Enemy 부모 클래스와 하위 몬스터 클래스 구현
-- IDamageable 인터페이스 적용
-- enum을 활용한 게임 상태 관리
-[ 매니저 구조 설계 ]
-- GameManager / WaveManager 역할 분리</t>
+   • Enemy 부모 클래스와 IDamageable 인터페이스 적용</t>
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
     </row>
-    <row r="16" ht="108" customHeight="1">
+    <row r="16" ht="99" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -879,17 +890,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>[ 코어 루프 완성 ]
-- 이동 → 자동사격 → 스폰 → 피격 → 게임오버 연결
-- 웨이브 스폰 로직 구현
-[ 무기 시스템 ]
-- 기본 무기 구현
-- 관통 무기 구현</t>
+          <t>[ 몬스터 구현 ]
+   • 몬스터 3종 구현 (기본 / 고속 / 탱커)
+   • 플레이어 추적 이동 로직
+[ 스폰 시스템 ]
+   • 화면 밖 스폰 포인트 배치
+   • 시간 경과에 따른 스폰 간격·능력치 강화</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
     </row>
-    <row r="17" ht="126" customHeight="1">
+    <row r="17" ht="114.5" customHeight="1">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -898,18 +909,18 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>[ 무기 시스템 확장 ]
-- 범위(폭발) 무기 구현
-- 다중 무기 동시 발사 구조
-[ 몬스터 다양화 ]
-- 돌진형 몬스터 구현
-- 원거리형 몬스터 구현
-- 탱커형 몬스터 구현</t>
+          <t>[ 무기 시스템 ]
+   • 회전 근접 무기 구현 (플레이어 주위를 도는 공격)
+   • 자동 조준 원거리 무기 구현
+   • 자동 공격 구조 이해
+[ 전투 처리 ]
+   • 피격 · 무적 시간 · 사망 처리
+   • 코어 루프 연결 (이동 → 자동공격 → 피격 → 게임오버)</t>
         </is>
       </c>
       <c r="D17" s="7" t="n"/>
     </row>
-    <row r="18" ht="108" customHeight="1">
+    <row r="18" ht="114.5" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>5개월</t>
@@ -922,22 +933,23 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>[ ScriptableObject 활용 ]
-- 데이터와 코드 분리 개념 이해
-- WeaponData / EnemyData 설계
-- 인스펙터 기반 밸런싱 실습
-[ 웨이브 데이터 설계 ]
-- WaveData 구성 및 난이도 곡선 설계</t>
+          <t>[ 경험치 시스템 ]
+   • 몬스터 처치 시 경험치 젬 드롭
+   • 자석 흡수 로직 구현
+[ 레벨업 ]
+   • 레벨업 곡선 설계
+   • Time.timeScale을 활용한 시간 정지
+   • 업그레이드 3택 1 선택 구조</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>게임 시스템 완성 및
+          <t>성장 시스템 완성 및
 UI·연출 구현</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="90" customHeight="1">
+    <row r="19" ht="130" customHeight="1">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -946,16 +958,19 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>[ 성장 시스템 ]
-- 업그레이드 3택 시스템 구현
-- 스탯 반영 및 신규 무기 획득 처리
+          <t>[ 성장 효과 반영 ]
+   • 업그레이드 8종 구현 (공격력·연사·관통·이동속도·자석 등)
+[ ScriptableObject 활용 ]
+   • 데이터와 코드 분리 개념 이해
+   • WeaponData / EnemyData / UpgradeData 설계
+   • 인스펙터 기반 밸런싱 실습
 [ 보스 구현 ]
-- 보스 패턴 구현</t>
+   • 시간대별 보스 3회 등장 구조</t>
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
     </row>
-    <row r="20" ht="108" customHeight="1">
+    <row r="20" ht="99" customHeight="1">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -965,16 +980,16 @@
       <c r="C20" s="4" t="inlineStr">
         <is>
           <t>[ 유니티 UI 기초 ]
-- Canvas와 Canvas Scaler를 활용한 해상도 대응
-- RectTransform / Anchor / Pivot 이해
-- TextMeshPro 및 한글 폰트 적용
+   • Canvas와 Canvas Scaler를 활용한 해상도 대응
+   • RectTransform / Anchor / Pivot 이해
+   • TextMeshPro 및 한글 폰트 적용
 [ HUD 구현 ]
-- 체력바 / 웨이브 / 잔여 몬스터 수 표시</t>
+   • 체력바 / 경험치바 / 레벨 / 생존 시간 / 처치 수 표시</t>
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
     </row>
-    <row r="21" ht="162" customHeight="1">
+    <row r="21" ht="145.5" customHeight="1">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -984,19 +999,19 @@
       <c r="C21" s="4" t="inlineStr">
         <is>
           <t>[ 게임 화면 구성 ]
-- 업그레이드 선택창 구현
-- 타이틀 / 결과 화면 제작
-- 씬 전환 및 데이터 유지 처리
-- Time.timeScale을 활용한 일시정지
+   • 레벨업 선택창 구현
+   • 타이틀 / 결과 화면 제작
+   • 씬 전환 및 데이터 유지 처리
+   • 일시정지 처리
 [ 연출과 사운드 ]
-- 파티클 시스템 기초
-- 카메라 셰이크 · 히트스톱 타격감 구현
-- AudioSource를 활용한 효과음 적용</t>
+   • 파티클 시스템 기초
+   • 카메라 셰이크 · 히트스톱 타격감 구현
+   • AudioSource를 활용한 효과음 적용</t>
         </is>
       </c>
       <c r="D21" s="7" t="n"/>
     </row>
-    <row r="22" ht="162" customHeight="1">
+    <row r="22" ht="145.5" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>6개월</t>
@@ -1010,14 +1025,14 @@
       <c r="C22" s="4" t="inlineStr">
         <is>
           <t>[ 성능 최적화 ]
-- 다량 오브젝트 생성 시 성능 저하 현상 확인
-- 프로파일러를 활용한 원인 분석
-- Instantiate / Destroy 비용 이해
-- 몬스터 · 총알 오브젝트 풀링 구현
+   • 다량 오브젝트 생성 시 성능 저하 현상 확인
+   • 프로파일러를 활용한 원인 분석
+   • Instantiate / Destroy 비용 이해
+   • 몬스터 · 총알 · 젬 오브젝트 풀링 구현
 [ 밸런싱 및 빌드 ]
-- 데이터 조정 및 교차 플레이 피드백
-- Player Settings 및 PC 빌드 산출
-- 빌드 결과물 상호 테스트 및 프로젝트 백업</t>
+   • 데이터 조정 및 교차 플레이 피드백
+   • Player Settings 및 PC 빌드 산출
+   • 빌드 결과물 상호 테스트 및 프로젝트 백업</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1027,7 +1042,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="144" customHeight="1">
+    <row r="23" ht="130" customHeight="1">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -1037,18 +1052,18 @@
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t>[ 멀티플레이 개념 이해 ]
-- 호스트 / 클라이언트 구조 이해
-- 네트워크 동기화의 필요성
+   • 호스트 / 클라이언트 구조 이해
+   • 네트워크 동기화의 필요성
 [ Netcode for GameObjects 기초 ]
-- NGO 설치 및 NetworkManager 설정
-- NetworkObject 등록과 로컬 접속 실습
+   • NGO 설치 및 NetworkManager 설정
+   • NetworkObject 등록과 로컬 접속 실습
 [ 멀티 테스트 환경 구축 ]
-- Multiplayer Play Mode 가상 플레이어 설정</t>
+   • Multiplayer Play Mode 가상 플레이어 설정</t>
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
     </row>
-    <row r="24" ht="108" customHeight="1">
+    <row r="24" ht="114.5" customHeight="1">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -1057,18 +1072,19 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>[ 멀티 테스트 환경 활용 ]
-- 가상 플레이어 기반 2인 테스트 실습
-[ 위치 동기화 ]
-- NetworkTransform을 활용한 이동 동기화
+          <t>[ 위치 동기화 ]
+   • 가상 플레이어 기반 2인 테스트 실습
+   • NetworkTransform을 활용한 이동 동기화
 [ 소유권 처리 ]
-- IsOwner를 활용한 입력 권한 분리</t>
+   • IsOwner를 활용한 입력 권한 분리
+[ 상태 동기화 기초 ]
+   • NetworkVariable을 활용한 체력·레벨 동기화</t>
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
     </row>
-    <row r="25" ht="108" customHeight="1">
-      <c r="A25" s="7" t="n"/>
+    <row r="25" ht="114.5" customHeight="1">
+      <c r="A25" s="6" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>24주차</t>
@@ -1076,48 +1092,45 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>[ 상태 동기화 ]
-- NetworkVariable을 활용한 체력·웨이브 동기화
-- Rpc를 활용한 클라이언트-서버 통신
-[ 서버 권한 처리 ]
-- 호스트 전용 몬스터 스폰 구현
-- 서버 기반 피격 판정 처리</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="144" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+          <t>[ 서버 권한 처리 ]
+   • Rpc를 활용한 클라이언트-서버 통신
+   • 호스트 전용 몬스터 스폰 구현
+   • 경험치 젬 생성·획득의 서버 처리
+   • 서버 기반 피격 판정
+[ 협동 카메라 ]
+   • 두 플레이어를 함께 담는 카메라 설계</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="145.5" customHeight="1">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>25주차</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>[ 협동 전용 기능 ]
+   • 협동 카메라 마무리 (거리 기반 줌 조정)
+   • 다운 및 동료 부활 구현
+   • 레벨업 시 양쪽 시간 정지 처리
+[ 접속 처리 ]
+   • Relay를 활용한 접속 코드 입장 구현
+[ 싱글·협동 모드 통합 ]
+   • 타이틀 [혼자 하기] / [같이 하기] 분기 처리
+   • 원격 합동 플레이 테스트 및 최종 검증</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="114.5" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>7개월</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>25주차</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>[ 접속 처리 ]
-- Relay를 활용한 접속 코드 입장 구현
-[ 싱글·협동 모드 통합 ]
-- 타이틀 [혼자 하기] / [같이 하기] 분기 처리
-- 싱글 모드를 호스트 1인 세션으로 통합
-- 원격 합동 플레이 테스트 및 버그 수정
-[ 최종 빌드 ]
-- 싱글·협동 동작 최종 검증 및 빌드 산출</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>협동 모드 완성 ·
-배포 및 최종 발표</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="108" customHeight="1">
-      <c r="A27" s="6" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>26주차</t>
@@ -1126,16 +1139,22 @@
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>[ 배포 ]
-- itch.io 업로드 및 공유 링크 발급
-- 시연 영상 · GIF 제작
-- 게임 소개글 작성
+   • 최종 빌드 산출 (싱글 · 협동 동작 확인)
+   • itch.io 업로드 및 공유 링크 발급
+   • 시연 영상 · GIF 제작
+   • 게임 소개글 작성
 [ 최종 발표 ]
-- 1인 시연 발표 및 Q&amp;A</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="72" customHeight="1">
+   • 1인 시연 발표 및 Q&amp;A</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>배포 · 발표 및
+결과물 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="68" customHeight="1">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -1145,14 +1164,14 @@
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>[ 진도 보완 ]
-- 미완성 기능 보완 및 개별 지원
+   • 미완성 기능 보완 및 개별 지원
 [ 개인 확장 ]
-- 심화 과제 구현 (추가 무기 · 몬스터 · 모드)</t>
+   • 심화 과제 구현 (추가 무기 · 몬스터 · 업그레이드)</t>
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29" ht="52.5" customHeight="1">
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -1162,8 +1181,8 @@
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t>[ 결과물 정리 ]
-- 프로젝트 문서화 및 산출물 정리
-- 최종 백업 및 과정 마무리</t>
+   • 프로젝트 문서화 및 산출물 정리
+   • 최종 백업 및 과정 마무리</t>
         </is>
       </c>
       <c r="D29" s="7" t="n"/>
@@ -1172,19 +1191,19 @@
   <mergeCells count="15">
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="D14:D17"/>
-    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="A22:A26"/>
     <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D22:D26"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D26:D29"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
+    <mergeCell ref="D27:D29"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="D2:D5"/>
-    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A27:A29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1196,11 +1215,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1286,123 +1305,131 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>타이틀에서 [혼자 하기] / [같이 하기]를 모두 지원하는 2D 협동 웨이브 디펜스</t>
+          <t>웨이브 브레이커 — 타이틀에서 [혼자 하기] / [같이 하기]를 모두 지원하는 2D 로그라이크 서바이버(뱀서라이크)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>사용 엔진</t>
+          <t>게임 규칙</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Unity 6 LTS + C# / 개발도구 Visual Studio</t>
+          <t>10분 생존 + 최종 보스 격파 / 무한 맵 / 자동 공격 / 경험치 젬 → 레벨업 3택1 / 보스 3회(3·6·10분)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>사용 엔진</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Netcode for GameObjects + Relay / 로컬 테스트는 Multiplayer Play Mode</t>
+          <t>Unity 6000.5.4f1 + C# / 개발도구 Visual Studio</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>리소스</t>
+          <t>렌더 파이프라인</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Kenney CC0 팩 (출처 표기 불필요, 상업 이용 및 포트폴리오 사용 가능)</t>
+          <t>URP 17.5.0 (Unity 6 2D 템플릿 기본값). URP 기능은 가르치지 않으며 9주차에 Sorting Layer만 다룸</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr"/>
-      <c r="B14" s="10" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Input System 패키지는 설치되어 있으나 수업은 구 Input Manager(Input.GetAxisRaw)로 진행 (Active Input Handling = Both)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>핵심 설계 ①</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>21주차에 싱글 게임을 완성·빌드·백업한다. 네트워크는 그 위에 얹는 별도 단계 — 멀티가 실패해도 전원이 완성작을 보유</t>
+          <t>Netcode for GameObjects + Relay / 로컬 테스트는 Multiplayer Play Mode</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>핵심 설계 ②</t>
+          <t>리소스</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>구간마다 스냅샷 프로젝트를 배포해 뒤처진 수강생이 정상 합류하게 한다</t>
+          <t>Kenney CC0 팩 (출처 표기 불필요, 상업 이용 및 포트폴리오 사용 가능)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>핵심 설계 ③</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>미션은 필수 / 도전 2단계로 운영해 수강생 간 진도 편차를 흡수한다</t>
-        </is>
-      </c>
+      <c r="A17" s="11" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr"/>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>핵심 설계 ①</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>21주차에 싱글 게임을 완성·빌드·백업한다. 네트워크는 그 위에 얹는 별도 단계 — 멀티가 실패해도 전원이 완성작을 보유</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>축소 순서</t>
+          <t>핵심 설계 ②</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>진도가 밀릴 경우: ①폭발탄 ②보스 ③업그레이드 8→5종 ④탱커형 몬스터 ⑤웨이브 10→7 순으로 축소</t>
+          <t>구간마다 스냅샷 프로젝트를 배포해 뒤처진 수강생이 정상 합류하게 한다</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>절대 유지</t>
+          <t>핵심 설계 ③</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>업그레이드 3택 시스템 / 21주차 싱글 빌드·백업 / 동료 부활 메커닉</t>
+          <t>미션은 필수 / 도전 2단계로 운영해 수강생 간 진도 편차를 흡수한다</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>추가 여유분</t>
+          <t>핵심 설계 ④</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>부족 시 미니게임 3개 → 2개(①③)로 축소하여 5회차 회수 가능</t>
+          <t>오브젝트 풀링은 21주차에 도입한다. 렉을 먼저 겪게 한 뒤 해결책으로 제시</t>
         </is>
       </c>
     </row>
@@ -1413,86 +1440,62 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>C# 선행 리스크</t>
+          <t>축소 순서</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>1~4주차 콘솔 위주 진행으로 비대면 노베이스 이탈 위험이 가장 높은 구간</t>
+          <t>진도가 밀릴 경우: ①보스 II·III ②몬스터 3종→2종 ③업그레이드 8종→4종 ④사운드 ⑤협동 부활 ⑥협동 전체(싱글 종강, 최후의 수단)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>대응 ①</t>
+          <t>절대 유지</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>1주차 첫 회차에 최종 결과물을 먼저 시연한다</t>
+          <t>무한 맵 / 레벨업 3택 / 자동 공격 / 오브젝트 풀링 / 21주차 싱글 빌드·백업</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>대응 ②</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>매주 마지막 회차에 결과물 발표 자리를 만든다</t>
-        </is>
-      </c>
+      <c r="A25" s="11" t="inlineStr"/>
+      <c r="B25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>대응 ③</t>
+          <t>제외한 문법</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>콘솔 실습 예제를 게임 문맥으로 구성한다(체력·데미지 계산, 몬스터 스탯 출력 등)</t>
+          <t>구조체(struct) / 템플릿(제네릭) 클래스 / 연산자 오버로딩</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr"/>
-      <c r="B27" s="10" t="inlineStr"/>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>제외 사유</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>제작할 게임에서 사용처가 없고 노베이스 대상 추상도가 높음. 필요 시 4주차 또는 27주차 보완 구간에 편성 가능</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>제외한 문법</t>
+          <t>포함 확인</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>구조체(struct) / 템플릿(제네릭) 클래스 / 연산자 오버로딩</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>제외 사유</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>제작할 게임에서 사용처가 없고 노베이스 대상 추상도가 높음. 필요 시 4주차 또는 27주차 보완 구간에 편성 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>포함 확인</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>property, static, switch, enum, 인터페이스, 다형성, Visual Studio 디버깅 모두 포함</t>
         </is>
